--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1196,138 +1196,118 @@
       </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>2026-08-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr"/>
       <c r="G3" s="64" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="n">
+      <c r="A4" s="78" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="80" t="inlineStr">
         <is>
+          <t>PS5-03-20 - FZ-20 - Emergency Diesel Generator Enclosure</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone C</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>2026-08-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr"/>
+      <c r="G4" s="64" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="80" t="inlineStr">
+        <is>
+          <t>PS5-05-01 - Emergency Diesel Generator Package</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone C</t>
+        </is>
+      </c>
+      <c r="E5" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL(22-08-2026)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr"/>
+      <c r="G5" s="64" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="80" t="inlineStr">
+        <is>
+          <t>PS5-05-02 - Emergency Diesel Generator Package (UCP)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone C</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr"/>
+      <c r="G6" s="64" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="80" t="inlineStr">
+        <is>
           <t>PS5-06-02 - AC UPS - Power Generator Building</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="64" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="82" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="80" t="inlineStr">
-        <is>
-          <t>PS5-09-05 - HVAC for EITS Building</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone A</t>
-        </is>
-      </c>
-      <c r="E5" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G5" s="64" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="82" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-01 - Power Generation Package A</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E6" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="64" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="82" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E7" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F7" s="23" t="inlineStr"/>
       <c r="G7" s="64" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1336,17 +1316,17 @@
       </c>
       <c r="B8" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-09-05 - HVAC for EITS Building</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone B</t>
+          <t>PS5 - Milestone A</t>
         </is>
       </c>
       <c r="E8" s="65" t="inlineStr">
@@ -1354,11 +1334,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F8" s="23" t="inlineStr"/>
       <c r="G8" s="64" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1367,12 +1343,12 @@
       </c>
       <c r="B9" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-04 - Power Generation Package B</t>
+          <t>PS5-60-01 - Power Generation Package A</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -1385,25 +1361,21 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F9" s="23" t="inlineStr"/>
       <c r="G9" s="64" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="n">
+      <c r="A10" s="78" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
+          <t>PS5-60-02 - Power Gen Package A (UCP)</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
@@ -1411,16 +1383,12 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr"/>
       <c r="G10" s="64" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1429,17 +1397,17 @@
       </c>
       <c r="B11" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
+          <t>PS5-60-03 - Power Gen Package A Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone D</t>
+          <t>PS5 - Milestone B</t>
         </is>
       </c>
       <c r="E11" s="65" t="inlineStr">
@@ -1447,11 +1415,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F11" s="23" t="inlineStr"/>
       <c r="G11" s="64" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1460,12 +1424,12 @@
       </c>
       <c r="B12" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+          <t>PS5-60-04 - Power Generation Package B</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
@@ -1473,16 +1437,12 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E12" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr"/>
       <c r="G12" s="64" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1491,12 +1451,12 @@
       </c>
       <c r="B13" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-27 - Compressed Air Starting Skid</t>
+          <t>PS5-60-05 - Power Gen Package B (UCP)</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
@@ -1509,11 +1469,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F13" s="23" t="inlineStr"/>
       <c r="G13" s="64" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1522,60 +1478,52 @@
       </c>
       <c r="B14" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
+          <t>PS5-60-12 - Power Gen Package D Generator Auxiliary MCCs &amp; DBs</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
+          <t>PS5 - Milestone D</t>
+        </is>
+      </c>
+      <c r="E14" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr"/>
+      <c r="G14" s="64" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>PS5-60-26 - Instrument Air Compressor Skid</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E14" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" s="64" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="82" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E15" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr"/>
       <c r="G15" s="64" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1584,12 +1532,12 @@
       </c>
       <c r="B16" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+          <t>PS5-60-27 - Compressed Air Starting Skid</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -1597,16 +1545,12 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E16" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr"/>
       <c r="G16" s="64" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1615,12 +1559,12 @@
       </c>
       <c r="B17" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+          <t>PS5-60-28 - Air Receiver A &amp; Air Regulator A</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -1628,16 +1572,12 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E17" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E17" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr"/>
       <c r="G17" s="64" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1646,153 +1586,133 @@
       </c>
       <c r="B18" s="80" t="inlineStr">
         <is>
+          <t>PS5-60-29 - Air Receiver B &amp; Air Regulator B</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr"/>
+      <c r="G18" s="64" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="78" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="80" t="inlineStr">
+        <is>
+          <t>PS5-60-35 - Injector Tip Cooling Module A</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr"/>
+      <c r="G19" s="64" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="78" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>PS5-60-36 - Injector Tip Cooling Module B</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr"/>
+      <c r="G20" s="64" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="80" t="inlineStr">
+        <is>
           <t>PS5-60-42 - Oil Mist Separator Skid PS5-60-VS-9100A</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E18" s="67" t="inlineStr">
+      <c r="E21" s="67" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" s="64" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="82" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="80" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr"/>
+      <c r="G21" s="64" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="78" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="80" t="inlineStr">
         <is>
           <t>PS5-60-43 - Oil Mist Separator Skid PS5-60-VS-9100B</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G19" s="64" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="82" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E20" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G20" s="64" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="82" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E21" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G21" s="64" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="82" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="80" t="inlineStr">
-        <is>
-          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>PS5 - Milestone B</t>
-        </is>
-      </c>
-      <c r="E22" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F22" s="23" t="inlineStr"/>
       <c r="G22" s="64" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1801,12 +1721,12 @@
       </c>
       <c r="B23" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
+          <t>PS5-60-49 - Lube Oil Separator Module PS5-60-UO-81100A</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -1819,11 +1739,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F23" s="23" t="inlineStr"/>
       <c r="G23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1832,12 +1748,12 @@
       </c>
       <c r="B24" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
+          <t>PS5-60-50 - Lube Oil Separator Module PS5-60-UO-81100B</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -1850,11 +1766,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F24" s="23" t="inlineStr"/>
       <c r="G24" s="64" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1863,12 +1775,12 @@
       </c>
       <c r="B25" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
+          <t>PS5-60-56 - Fuel Conditioning Module PS5-60-UZ-8900A</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -1883,7 +1795,7 @@
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>THERMAL INSULATION</t>
         </is>
       </c>
       <c r="G25" s="64" t="inlineStr"/>
@@ -1894,12 +1806,12 @@
       </c>
       <c r="B26" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-70 - Engine A Cooling system</t>
+          <t>PS5-60-57 - Fuel Conditioning Module PS5-60-UZ-8900A (UCP)</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -1912,11 +1824,7 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F26" s="23" t="inlineStr"/>
       <c r="G26" s="64" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1925,12 +1833,12 @@
       </c>
       <c r="B27" s="80" t="inlineStr">
         <is>
-          <t>PS5-60-71 - Engine B Cooling system</t>
+          <t>PS5-60-58 - Fuel Conditioning Module PS5-60-UZ-8900B</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -1945,7 +1853,7 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>THERMAL INSULATION</t>
         </is>
       </c>
       <c r="G27" s="64" t="inlineStr"/>
@@ -1956,12 +1864,12 @@
       </c>
       <c r="B28" s="80" t="inlineStr">
         <is>
-          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
+          <t>PS5-60-59 - Fuel Conditioning Module PS5-60-UZ-8900B (UCP)</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
@@ -1969,16 +1877,12 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E28" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E28" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr"/>
       <c r="G28" s="64" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1987,12 +1891,12 @@
       </c>
       <c r="B29" s="80" t="inlineStr">
         <is>
-          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+          <t>PS5-60-70 - Engine A Cooling system</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -2005,65 +1909,61 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="F29" s="23" t="inlineStr"/>
       <c r="G29" s="64" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="78" t="n">
+      <c r="A30" s="82" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="80" t="inlineStr">
         <is>
-          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+          <t>PS5-60-71 - Engine B Cooling system</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr"/>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E30" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr"/>
       <c r="G30" s="64" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="82" t="n">
+      <c r="A31" s="78" t="n">
         <v>29</v>
       </c>
       <c r="B31" s="80" t="inlineStr">
         <is>
-          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+          <t>PS5-61-05 - 0.4kV Switchboard Power Generator Building (PS5-61-IK-0003)</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>58%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone H</t>
-        </is>
-      </c>
-      <c r="E31" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr"/>
       <c r="G31" s="64" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2072,33 +1972,106 @@
       </c>
       <c r="B32" s="80" t="inlineStr">
         <is>
+          <t>PS5-63-03 - Electrical Earthing - Generator Building</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E32" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr"/>
+      <c r="G32" s="64" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="78" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="80" t="inlineStr">
+        <is>
+          <t>PS5-63-04 - Electrical Earthing - EITS Building</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr"/>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr"/>
+      <c r="G33" s="64" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="82" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="80" t="inlineStr">
+        <is>
+          <t>PS5-71-09 - CFO Pre-Pressure Modules (UCP)</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone H</t>
+        </is>
+      </c>
+      <c r="E34" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr"/>
+      <c r="G34" s="64" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="78" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="80" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>PS5 - Milestone A</t>
         </is>
       </c>
-      <c r="E32" s="67" t="inlineStr">
+      <c r="E35" s="67" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G32" s="64" t="inlineStr"/>
+      <c r="F35" s="23" t="inlineStr"/>
+      <c r="G35" s="64" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G32"/>
+  <autoFilter ref="A2:G35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2133,6 +2106,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIDMAP" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'7 · COMPLETE'!$A$2:$G$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1113,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2044,34 +2044,65 @@
       <c r="G34" s="64" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="78" t="n">
-        <v>33</v>
+      <c r="A35" s="82" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B35" s="80" t="inlineStr">
         <is>
+          <t>PS5-78-01 - Lifting and handling equipment</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>PS5 - Milestone E</t>
+        </is>
+      </c>
+      <c r="E35" s="65" t="inlineStr">
+        <is>
+          <t>PARTIAL(05-03-2026)</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="64" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="78" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" s="80" t="inlineStr">
+        <is>
           <t>PS5-91-01 - Multicore cables &amp; JB</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>PS5 - Milestone A</t>
         </is>
       </c>
-      <c r="E35" s="67" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F35" s="23" t="inlineStr"/>
-      <c r="G35" s="64" t="inlineStr"/>
+      <c r="F36" s="23" t="inlineStr"/>
+      <c r="G36" s="64" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G35"/>
+  <autoFilter ref="A2:G36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/EXCEL/7 - COMPLETE.xlsx
+++ b/EXCEL/7 - COMPLETE.xlsx
@@ -67,7 +67,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFc00000"/>
+      <color rgb="FFed7d31"/>
       <sz val="10"/>
     </font>
     <font>
@@ -79,7 +79,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFed7d31"/>
+      <color rgb="FFc00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -674,22 +674,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -701,7 +701,7 @@
     <xf numFmtId="0" fontId="5" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1199,7 +1199,11 @@
           <t>2026-08-08 00:00:00</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G3" s="64" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1226,7 +1230,11 @@
           <t>2026-08-07 00:00:00</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G4" s="64" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1248,12 +1256,16 @@
           <t>PS5 - Milestone C</t>
         </is>
       </c>
-      <c r="E5" s="65" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>PARTIAL(22-08-2026)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G5" s="64" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1275,12 +1287,16 @@
           <t>PS5 - Milestone C</t>
         </is>
       </c>
-      <c r="E6" s="67" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G6" s="64" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1302,12 +1318,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E7" s="67" t="inlineStr">
+      <c r="E7" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G7" s="64" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1329,12 +1349,16 @@
           <t>PS5 - Milestone A</t>
         </is>
       </c>
-      <c r="E8" s="65" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G8" s="64" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1348,7 +1372,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -1356,12 +1380,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E9" s="65" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G9" s="64" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1383,12 +1411,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E10" s="67" t="inlineStr">
+      <c r="E10" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G10" s="64" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1410,12 +1442,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E11" s="65" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr"/>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G11" s="64" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1429,7 +1465,7 @@
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
@@ -1437,12 +1473,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E12" s="65" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G12" s="64" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1464,12 +1504,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E13" s="65" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G13" s="64" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1491,12 +1535,16 @@
           <t>PS5 - Milestone D</t>
         </is>
       </c>
-      <c r="E14" s="65" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G14" s="64" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1518,16 +1566,20 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E15" s="67" t="inlineStr">
+      <c r="E15" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr"/>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G15" s="64" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="82" t="n">
+      <c r="A16" s="78" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="80" t="inlineStr">
@@ -1537,7 +1589,7 @@
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -1545,12 +1597,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E16" s="65" t="inlineStr">
+      <c r="E16" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G16" s="64" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1572,12 +1628,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E17" s="65" t="inlineStr">
+      <c r="E17" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G17" s="64" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1599,12 +1659,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E18" s="65" t="inlineStr">
+      <c r="E18" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr"/>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G18" s="64" t="inlineStr"/>
     </row>
     <row r="19">
@@ -1626,12 +1690,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E19" s="67" t="inlineStr">
+      <c r="E19" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G19" s="64" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1653,12 +1721,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E20" s="67" t="inlineStr">
+      <c r="E20" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr"/>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G20" s="64" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1680,12 +1752,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E21" s="67" t="inlineStr">
+      <c r="E21" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G21" s="64" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1707,12 +1783,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E22" s="67" t="inlineStr">
+      <c r="E22" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G22" s="64" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1726,7 +1806,7 @@
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -1734,12 +1814,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E23" s="65" t="inlineStr">
+      <c r="E23" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G23" s="64" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1753,7 +1837,7 @@
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -1761,12 +1845,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E24" s="65" t="inlineStr">
+      <c r="E24" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr"/>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G24" s="64" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1780,7 +1868,7 @@
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -1788,7 +1876,7 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E25" s="65" t="inlineStr">
+      <c r="E25" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1819,12 +1907,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E26" s="65" t="inlineStr">
+      <c r="E26" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr"/>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G26" s="64" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1838,7 +1930,7 @@
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -1846,7 +1938,7 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E27" s="65" t="inlineStr">
+      <c r="E27" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1877,16 +1969,20 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E28" s="65" t="inlineStr">
+      <c r="E28" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr"/>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G28" s="64" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="82" t="n">
+      <c r="A29" s="78" t="n">
         <v>27</v>
       </c>
       <c r="B29" s="80" t="inlineStr">
@@ -1896,7 +1992,7 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -1904,16 +2000,20 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E29" s="65" t="inlineStr">
+      <c r="E29" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F29" s="23" t="inlineStr"/>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G29" s="64" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="82" t="n">
+      <c r="A30" s="78" t="n">
         <v>28</v>
       </c>
       <c r="B30" s="80" t="inlineStr">
@@ -1923,7 +2023,7 @@
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
@@ -1931,12 +2031,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E30" s="65" t="inlineStr">
+      <c r="E30" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G30" s="64" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1958,12 +2062,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E31" s="67" t="inlineStr">
+      <c r="E31" s="66" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="F31" s="23" t="inlineStr"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G31" s="64" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1985,12 +2093,16 @@
           <t>PS5 - Milestone B</t>
         </is>
       </c>
-      <c r="E32" s="65" t="inlineStr">
+      <c r="E32" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr"/>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G32" s="64" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2035,48 +2147,52 @@
           <t>PS5 - Milestone H</t>
         </is>
       </c>
-      <c r="E34" s="65" t="inlineStr">
+      <c r="E34" s="53" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr"/>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G34" s="64" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="82" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A35" s="78" t="n">
+        <v>33</v>
       </c>
       <c r="B35" s="80" t="inlineStr">
         <is>
-          <t>PS5-78-01 - Lifting and handling equipment</t>
+          <t>PS5-71-22 - Diesel Fuel Pre Pressure Module</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>PS5 - Milestone E</t>
-        </is>
-      </c>
-      <c r="E35" s="65" t="inlineStr">
-        <is>
-          <t>PARTIAL(05-03-2026)</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="64" t="n"/>
+          <t>PS5 - Milestone B</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" s="64" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A36" s="78" t="n">
+        <v>34</v>
       </c>
       <c r="B36" s="80" t="inlineStr">
         <is>
@@ -2093,12 +2209,16 @@
           <t>PS5 - Milestone A</t>
         </is>
       </c>
-      <c r="E36" s="67" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr"/>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="G36" s="64" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2140,6 +2260,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
